--- a/src/main/resources/Scheduler.xlsx
+++ b/src/main/resources/Scheduler.xlsx
@@ -1,327 +1,200 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18530" windowHeight="6950"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18530" windowHeight="6950" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Job-Add" sheetId="3" r:id="rId1"/>
-    <sheet name="Sceduler-Detail" sheetId="2" r:id="rId2"/>
+    <sheet name="Job-Add" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scheduler-Detail" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
-  <si>
-    <t>Job Name</t>
-  </si>
-  <si>
-    <t>Task Detail Id</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>End Date</t>
-  </si>
-  <si>
-    <t>Start Time</t>
-  </si>
-  <si>
-    <t>Frequency</t>
-  </si>
-  <si>
-    <t>Recurrence</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Email Job Complete</t>
-  </si>
-  <si>
-    <t>Email Job Fail</t>
-  </si>
-  <si>
-    <t>Email Job Skip</t>
-  </si>
-  <si>
-    <t>Filed Name</t>
-  </si>
-  <si>
-    <t>Required</t>
-  </si>
-  <si>
-    <t>Detail</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>Job Name must be unique</t>
-  </si>
-  <si>
-    <t>Trigger Detail</t>
-  </si>
-  <si>
-    <t>Trigger Detail must be match with the target class</t>
-  </si>
-  <si>
-    <t>Start Date Pattern YYYY-MM-dd</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>End Date Pattern YYYY-MM-dd</t>
-  </si>
-  <si>
-    <t>Start Time HH:MM</t>
-  </si>
-  <si>
-    <t>Frequency Mint,Hr,Daily,Weekly,Monthly</t>
-  </si>
-  <si>
-    <t>Recurrence Add the mint or hr for mint(1-59) or for hr(1-12) or weekly (Sunday-Monday) or monthly (1-31) any 1 day</t>
-  </si>
-  <si>
-    <t>Thread Priority</t>
-  </si>
-  <si>
-    <t>Email job complete</t>
-  </si>
-  <si>
-    <t>Check True|False can be use to  email</t>
-  </si>
-  <si>
-    <t>Email job fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email job skip </t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>IF the process in running state then skip the next run and update the time with the next interval</t>
-  </si>
-  <si>
-    <t>Mint</t>
-  </si>
-  <si>
-    <t>5,10,15,20,25,30,35,40,45,50,55</t>
-  </si>
-  <si>
-    <t>Hr</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>Weekly</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="23">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF202124"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF202124"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="37">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -687,180 +560,180 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -916,11 +789,74 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1120,257 +1056,380 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.72727272727273" customWidth="1"/>
-    <col min="2" max="2" width="13.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="10.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="9.18181818181818" customWidth="1"/>
-    <col min="5" max="6" width="10.2727272727273" customWidth="1"/>
-    <col min="7" max="7" width="11.0909090909091" customWidth="1"/>
-    <col min="8" max="8" width="7.72727272727273" customWidth="1"/>
-    <col min="9" max="9" width="18.5454545454545" customWidth="1"/>
-    <col min="10" max="10" width="12.6363636363636" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
+    <col width="9.72727272727273" customWidth="1" min="1" max="1"/>
+    <col width="13.1818181818182" customWidth="1" min="2" max="2"/>
+    <col width="10.1818181818182" customWidth="1" min="3" max="3"/>
+    <col width="9.18181818181818" customWidth="1" min="4" max="4"/>
+    <col width="10.2727272727273" customWidth="1" min="5" max="6"/>
+    <col width="11.0909090909091" customWidth="1" min="7" max="7"/>
+    <col width="7.72727272727273" customWidth="1" min="8" max="8"/>
+    <col width="18.5454545454545" customWidth="1" min="9" max="9"/>
+    <col width="12.6363636363636" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Job Name</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Task Detail Id</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Start Time</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Recurrence</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Email Job Complete</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Email Job Fail</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Email Job Skip</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C1001"/>
-  <sheetFormatPr defaultColWidth="14.4272727272727" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.4272727272727" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.8636363636364" customWidth="1"/>
-    <col min="2" max="2" width="12.2909090909091" customWidth="1"/>
-    <col min="3" max="3" width="103.290909090909" customWidth="1"/>
-    <col min="4" max="26" width="8.70909090909091" customWidth="1"/>
+    <col width="19.8636363636364" customWidth="1" min="1" max="1"/>
+    <col width="12.2909090909091" customWidth="1" min="2" max="2"/>
+    <col width="103.290909090909" customWidth="1" min="3" max="3"/>
+    <col width="8.709090909090911" customWidth="1" min="4" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
+    <row r="1" ht="14.25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>15</v>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Job Name</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Job Name must be unique</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Task Detail Id</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Task Detail Id must reference an existing, active Source Task (see the dropdown on that column in Job-Add).</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Start Date Pattern YYYY-MM-dd</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>20</v>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>End Date Pattern YYYY-MM-dd</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Start Time</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Start Time HH:MM</t>
+        </is>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>22</v>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Frequency Mint,Hr,Daily,Weekly,Monthly</t>
+        </is>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>23</v>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Recurrence</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Recurrence: pick one value from the matching row below (Mint/Hr/Daily/Weekly/Monthly). For Weekly and Monthly this is "every N weeks/months" -- bulk upload does not support picking a specific weekday or day-of-month.</t>
+        </is>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>24</v>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Thread Priority</t>
+        </is>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>26</v>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Email job complete</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Check True|False can be use to  email</t>
+        </is>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>26</v>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Email job fail</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Check True|False can be use to  email</t>
+        </is>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1" spans="1:3">
-      <c r="A12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>26</v>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email job skip </t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Check True|False can be use to  email</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1"/>
     <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1" spans="2:3">
-      <c r="B15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>30</v>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>IF the process in running state then skip the next run and update the time with the next interval</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1" spans="2:3">
-      <c r="B17" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>32</v>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Mint</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>5,10,15,20,25,30,35,40,45,50,55</t>
+        </is>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1" spans="2:3">
-      <c r="B18" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>34</v>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Hr</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1" spans="2:3">
-      <c r="B19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="11">
-        <v>1</v>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6</t>
+        </is>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1" spans="2:3">
-      <c r="B20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>37</v>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>1,2,3,4</t>
+        </is>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1" spans="2:3">
-      <c r="B21" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>37</v>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1"/>
@@ -2355,7 +2414,6 @@
     <row r="1001" ht="14.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="1"/>
 </worksheet>
 </file>